--- a/data/triangle_v10.xlsx
+++ b/data/triangle_v10.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\La Chouette\Python\AssembleurTriangles\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14E4D99-316A-441E-ADD7-8161B85FC846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E693AAE-16CE-4C03-B696-9B7D5FBD5767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="10350" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Triangles" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -157,31 +170,31 @@
     <t>Vézelay</t>
   </si>
   <si>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>Brétigny</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
     <t>Château-Gaillard</t>
   </si>
   <si>
-    <t>Brétigny</t>
-  </si>
-  <si>
     <t>Montereau</t>
   </si>
   <si>
-    <t>Metz</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Belle-Ile-en-Mer</t>
+    <t>Guérande</t>
   </si>
   <si>
     <t>Coetquidan</t>
   </si>
   <si>
-    <t>Chinon</t>
-  </si>
-  <si>
     <t>Rouen</t>
+  </si>
+  <si>
+    <t>Compiègne</t>
   </si>
   <si>
     <t>Domrémy</t>
@@ -209,6 +222,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1445,22 +1459,22 @@
         <v>46</v>
       </c>
       <c r="E26">
-        <v>4.96</v>
+        <v>71.540000000000006</v>
       </c>
       <c r="F26">
-        <v>8.6199999999999992</v>
+        <v>26.07</v>
       </c>
       <c r="G26">
-        <v>166.41</v>
+        <v>82.38</v>
       </c>
       <c r="H26">
-        <v>250.89</v>
+        <v>361.19</v>
       </c>
       <c r="I26">
         <v>160.16999999999999</v>
       </c>
       <c r="J26">
-        <v>92.36</v>
+        <v>345.66</v>
       </c>
       <c r="K26" t="s">
         <v>15</v>
@@ -1480,25 +1494,25 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>32.549999999999997</v>
+        <v>7.46</v>
       </c>
       <c r="F27">
-        <v>33.21</v>
+        <v>7.66</v>
       </c>
       <c r="G27">
-        <v>114.24</v>
+        <v>164.88</v>
       </c>
       <c r="H27">
-        <v>250.89</v>
+        <v>361.19</v>
       </c>
       <c r="I27">
-        <v>150.69999999999999</v>
+        <v>184.57</v>
       </c>
       <c r="J27">
-        <v>148.03</v>
+        <v>179.79</v>
       </c>
       <c r="K27" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.45">
@@ -1515,25 +1529,25 @@
         <v>49</v>
       </c>
       <c r="E28">
-        <v>7.46</v>
+        <v>32.549999999999997</v>
       </c>
       <c r="F28">
-        <v>7.66</v>
+        <v>33.21</v>
       </c>
       <c r="G28">
-        <v>164.88</v>
+        <v>114.24</v>
       </c>
       <c r="H28">
-        <v>361.19</v>
+        <v>250.89</v>
       </c>
       <c r="I28">
-        <v>184.57</v>
+        <v>150.69999999999999</v>
       </c>
       <c r="J28">
-        <v>179.79</v>
+        <v>148.03</v>
       </c>
       <c r="K28" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
@@ -1550,22 +1564,22 @@
         <v>50</v>
       </c>
       <c r="E29">
-        <v>133.97</v>
+        <v>67.16</v>
       </c>
       <c r="F29">
-        <v>24.95</v>
+        <v>72.17</v>
       </c>
       <c r="G29">
-        <v>21.08</v>
+        <v>40.68</v>
       </c>
       <c r="H29">
-        <v>361.19</v>
+        <v>250.89</v>
       </c>
       <c r="I29">
-        <v>423.61</v>
+        <v>366.43</v>
       </c>
       <c r="J29">
-        <v>722.75</v>
+        <v>354.74</v>
       </c>
       <c r="K29" t="s">
         <v>15</v>
@@ -1585,25 +1599,25 @@
         <v>52</v>
       </c>
       <c r="E30">
-        <v>13.12</v>
+        <v>53.04</v>
       </c>
       <c r="F30">
-        <v>10.7</v>
+        <v>49.95</v>
       </c>
       <c r="G30">
-        <v>156.18</v>
+        <v>77.010000000000005</v>
       </c>
       <c r="H30">
         <v>356.02</v>
       </c>
       <c r="I30">
-        <v>163.63</v>
+        <v>279.67</v>
       </c>
       <c r="J30">
-        <v>200.14</v>
+        <v>291.97000000000003</v>
       </c>
       <c r="K30" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
@@ -1620,22 +1634,22 @@
         <v>53</v>
       </c>
       <c r="E31">
-        <v>53.04</v>
+        <v>79.5</v>
       </c>
       <c r="F31">
-        <v>49.95</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="G31">
-        <v>77.010000000000005</v>
+        <v>60.7</v>
       </c>
       <c r="H31">
         <v>356.02</v>
       </c>
       <c r="I31">
-        <v>279.67</v>
+        <v>261.32</v>
       </c>
       <c r="J31">
-        <v>291.97000000000003</v>
+        <v>401.41</v>
       </c>
       <c r="K31" t="s">
         <v>11</v>
@@ -1652,25 +1666,25 @@
         <v>54</v>
       </c>
       <c r="D32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E32">
-        <v>105.98</v>
+        <v>7.07</v>
       </c>
       <c r="F32">
-        <v>23.84</v>
+        <v>154.15</v>
       </c>
       <c r="G32">
-        <v>50.18</v>
+        <v>18.78</v>
       </c>
       <c r="H32">
         <v>288.39</v>
       </c>
       <c r="I32">
-        <v>151.78</v>
+        <v>390.65</v>
       </c>
       <c r="J32">
-        <v>360.98</v>
+        <v>110.33</v>
       </c>
       <c r="K32" t="s">
         <v>11</v>
@@ -1687,25 +1701,25 @@
         <v>54</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E33">
-        <v>7.07</v>
+        <v>105.98</v>
       </c>
       <c r="F33">
-        <v>154.15</v>
+        <v>23.84</v>
       </c>
       <c r="G33">
-        <v>18.78</v>
+        <v>50.18</v>
       </c>
       <c r="H33">
         <v>288.39</v>
       </c>
       <c r="I33">
-        <v>390.65</v>
+        <v>151.78</v>
       </c>
       <c r="J33">
-        <v>110.33</v>
+        <v>360.98</v>
       </c>
       <c r="K33" t="s">
         <v>11</v>
